--- a/artfynd/Glesskallberget artfynd.xlsx
+++ b/artfynd/Glesskallberget artfynd.xlsx
@@ -7612,7 +7612,7 @@
         <v>113679611</v>
       </c>
       <c r="B70" t="n">
-        <v>79361</v>
+        <v>79405</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>113680972</v>
       </c>
       <c r="B72" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>113680973</v>
       </c>
       <c r="B73" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>113680974</v>
       </c>
       <c r="B74" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>113679613</v>
       </c>
       <c r="B78" t="n">
-        <v>79329</v>
+        <v>79373</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>113679614</v>
       </c>
       <c r="B109" t="n">
-        <v>79361</v>
+        <v>79405</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>113679625</v>
       </c>
       <c r="B110" t="n">
-        <v>79361</v>
+        <v>79405</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>113679627</v>
       </c>
       <c r="B111" t="n">
-        <v>79361</v>
+        <v>79405</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>113679626</v>
       </c>
       <c r="B120" t="n">
-        <v>79329</v>
+        <v>79373</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>113679622</v>
       </c>
       <c r="B124" t="n">
-        <v>80434</v>
+        <v>80488</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>113679624</v>
       </c>
       <c r="B125" t="n">
-        <v>80434</v>
+        <v>80488</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>113679623</v>
       </c>
       <c r="B127" t="n">
-        <v>80463</v>
+        <v>80493</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>122747407</v>
       </c>
       <c r="B130" t="n">
-        <v>80434</v>
+        <v>80488</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>113679615</v>
       </c>
       <c r="B168" t="n">
-        <v>79361</v>
+        <v>79405</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>113679616</v>
       </c>
       <c r="B175" t="n">
-        <v>79329</v>
+        <v>79373</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>113679618</v>
       </c>
       <c r="B180" t="n">
-        <v>80434</v>
+        <v>80488</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>113679617</v>
       </c>
       <c r="B182" t="n">
-        <v>80463</v>
+        <v>80493</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>113679621</v>
       </c>
       <c r="B184" t="n">
-        <v>79361</v>
+        <v>79405</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>113679620</v>
       </c>
       <c r="B185" t="n">
-        <v>80434</v>
+        <v>80488</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>113679619</v>
       </c>
       <c r="B186" t="n">
-        <v>80469</v>
+        <v>80499</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
